--- a/bom/BOM_LoraMesh Solar Bridge (433 and 868MHz) - Motherboard_PCB and Enclosure_2026-08-29.xlsx
+++ b/bom/BOM_LoraMesh Solar Bridge (433 and 868MHz) - Motherboard_PCB and Enclosure_2026-08-29.xlsx
@@ -70,16 +70,16 @@
     <t>2</t>
   </si>
   <si>
-    <t>BMP280</t>
-  </si>
-  <si>
-    <t>LGA-8_L2.5-W2.0-P0.65_AMP6127</t>
+    <t>BME280</t>
+  </si>
+  <si>
+    <t>LGA-8_BME280_BL</t>
   </si>
   <si>
     <t>Bosch(博世)</t>
   </si>
   <si>
-    <t>C83291</t>
+    <t>C92489</t>
   </si>
   <si>
     <t>3</t>
